--- a/upload/crib_2019.xlsx
+++ b/upload/crib_2019.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rb90efa73dba04b06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Re1a5a83c9c24423a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -60790,13 +60790,13 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1.02</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -60832,13 +60832,13 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -60874,13 +60874,13 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1.46</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -60916,13 +60916,13 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -61907,6 +61907,678 @@
       </x:c>
       <x:c s="8">
         <x:v>8</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>&gt; 15</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>100</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>I</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>0 a 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>9,3</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>II</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>6 a 10</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>55,9</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>III</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>11 a 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>73,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0.73</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>&gt; 15</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>100</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>I</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>0 a 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>9,3</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>II</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>6 a 10</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>55,9</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>III</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>11 a 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>73,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>&gt; 15</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>100</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>I</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>0 a 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>9,3</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>II</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>6 a 10</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>55,9</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>III</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>11 a 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>73,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>&gt; 15</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>100</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>I</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>0 a 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>9,3</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>II</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>6 a 10</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>55,9</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>III</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>11 a 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>73,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
